--- a/data/trans_dic/VUL_MENTALCOM-Edad-trans_dic.xlsx
+++ b/data/trans_dic/VUL_MENTALCOM-Edad-trans_dic.xlsx
@@ -583,40 +583,40 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>0.03482378136582487</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>0.1014673602543125</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.02601879605111057</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>0.02742139864693029</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.07441995311703159</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0</v>
+        <v>0.2822788973242764</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>0.02552385811589544</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>0.01919148763881961</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>0.05386282409916656</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>0.189629205946768</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>0.02577328961775728</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>0.02362486972863145</v>
       </c>
     </row>
     <row r="5">
@@ -626,18 +626,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n">
+        <v>0.007812429946099928</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.0594805646325724</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.00995139035998715</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.01248711735361344</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.03367234924002596</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.201934401327754</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.01062977116274955</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.007709601216125928</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.0278107029982033</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.1467998862127545</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.01313121119131604</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.01359824433972186</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -646,18 +670,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n">
+        <v>0.09947685406409269</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.1665545651954586</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.05626629985876849</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.05417315681975691</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.1462265029548334</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.3598309072478798</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.05542678461510223</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.03939027296033698</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.09946712301142775</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.2439031955722675</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.0458422557280041</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.04194333594081402</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -671,40 +719,40 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>0.0281736980989372</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0</v>
+        <v>0.1207215224977089</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>0.03283380204579113</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>0.01782686526384878</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>0.09354661700446407</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>0.2540194755566841</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>0.03868024028240983</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>0.02936989087011335</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>0.06224509758512396</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>0.1883932699367726</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0</v>
+        <v>0.03602208718869151</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
+        <v>0.02341820632828149</v>
       </c>
     </row>
     <row r="8">
@@ -714,18 +762,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n">
+        <v>0.007584256459816767</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.08449788378368632</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.01393340687565644</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.008449707056001976</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.05893438746012652</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.2003104706853671</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.019675565686608</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.01523147402192268</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.04127144185759259</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.1541203460231901</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.02184224080598623</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.01496299350985562</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -734,18 +806,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n">
+        <v>0.06719787204452082</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.1685403346146024</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.06326592472353085</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.03539902361563498</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.1441115969249517</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.3142088981419662</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.06824789688449662</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.05100776141925046</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.09322175338493503</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.2282389651812306</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0.05467556294131672</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0.0374285010018574</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -759,40 +855,40 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>0.05367562306928646</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>0.1682981244486502</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>0.02659438013363422</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>0.02024944073719653</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>0.07482333605344846</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>0.2173326684289111</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>0.06556611694757747</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>0.03543219884320826</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>0.06414927651396593</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>0.1920969007830266</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>0.0457297919541013</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>0.02820634175199006</v>
       </c>
     </row>
     <row r="11">
@@ -802,18 +898,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>0.03016359597954697</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.1248480189976409</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.01113323661574075</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.01016674700264487</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.05274061467838412</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.1691727353091488</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.04179826664948412</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.02266652380557408</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.04731484702290498</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.1598847582208294</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.03169922999227669</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0.01921814090548653</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -822,18 +942,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="n">
+        <v>0.09246128410029605</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.2195358404845028</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.04983479311268729</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.03667585381566058</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.1063585209026254</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.271218553881484</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.09630328805390621</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.05337235615463352</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.08735965085974182</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0.2312274806347301</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.06599651637212188</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.04059901845962403</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -847,40 +991,40 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>0.09181358974403463</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0</v>
+        <v>0.176359592773145</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>0.02253152704863432</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>0.0361997522493044</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>0.134134895101329</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>0.2754191835691445</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>0.0601137023516241</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>0.04632267511794191</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>0.1136201908632543</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>0.2262820296023883</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0</v>
+        <v>0.04084372924011182</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
+        <v>0.04142782963095774</v>
       </c>
     </row>
     <row r="14">
@@ -890,18 +1034,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="n">
+        <v>0.06397862250417859</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.1271826667654528</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.01010529897458529</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.02316982706844529</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.1096872769235678</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.2172752719920316</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.03752926843888929</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.03308091224230954</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.09208982370285317</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.1888699898223664</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.0275719255500253</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.03217278224934794</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -910,18 +1078,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="n">
+        <v>0.1287691435050083</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.2311450071754394</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.04003225118268547</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.0526274914954619</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.1641820785270118</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.347482986444697</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.08995500611855854</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.06511590832036925</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.1357804386339265</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.2713105675161171</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.0590250148754235</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.05283738459719851</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -935,40 +1127,40 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>0.09744515473179761</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0</v>
+        <v>0.1275758454978027</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>0.05812272278321026</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0</v>
+        <v>0.06794210963917256</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>0.1873241604989222</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0</v>
+        <v>0.2984023367392421</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0</v>
+        <v>0.08574741153832931</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0</v>
+        <v>0.08162366376779517</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>0.141767366264385</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>0.2201166176742828</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0</v>
+        <v>0.07227174425874372</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0</v>
+        <v>0.07537255979029178</v>
       </c>
     </row>
     <row r="17">
@@ -978,18 +1170,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="n">
+        <v>0.07069728992289687</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.08200948069109976</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.03433610026865779</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.04823999744392025</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.1539006665521632</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.2412035416654862</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.05942990776933141</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.06282466147099544</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.1208000811128217</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0.1804007516767732</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.05271377143728</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0.06107298476786893</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -998,18 +1214,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="n">
+        <v>0.1332702324579012</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.178243608903655</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.08998324097282022</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.09113928205953975</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.2235472194441377</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.3712873632810892</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.122468067719038</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.1042460989942442</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.1659391852982279</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.2713391075099954</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.09607237419252336</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0.09146851484663844</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1023,40 +1263,40 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>0.03213384530424398</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>0.1837097732146527</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>0.02353044451279828</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0</v>
+        <v>0.04304949383033387</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>0.1602558960790263</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0</v>
+        <v>0.2779538641096</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0</v>
+        <v>0.07627824999581283</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0</v>
+        <v>0.09322099337619301</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>0.1007958187729169</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0</v>
+        <v>0.236730570302163</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0</v>
+        <v>0.05123018282899636</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>0.06967658204233305</v>
       </c>
     </row>
     <row r="20">
@@ -1066,18 +1306,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="n">
+        <v>0.01544142101005374</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.1204593037179788</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0.0128428574204616</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.02839769261036018</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.1297447735267709</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.2015557315052187</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.0519190874810169</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.07162423072952638</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.08045271726691673</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.1841165899056721</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0.03795347019113535</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0.0552670321979931</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1086,18 +1350,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="n">
+        <v>0.05817494728136852</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.2741238305959369</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.04143730186690821</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.06538961515063796</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.1961092533656391</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.3744572570058962</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.1063930182283767</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.120968742892967</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.1243329714910863</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.300272349951361</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.06864818245141334</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0.08567688194364113</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1111,40 +1399,40 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>0.09323608284159071</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0</v>
+        <v>0.2136198628599572</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0</v>
+        <v>0.05684621974905935</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0</v>
+        <v>0.03776764804949036</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>0.1705882335176489</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>0.3855325392910053</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0</v>
+        <v>0.09786528187804445</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0</v>
+        <v>0.1409678141367103</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>0.140343280641974</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0</v>
+        <v>0.3206955025821487</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0</v>
+        <v>0.08137994404512226</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0</v>
+        <v>0.09930963948027643</v>
       </c>
     </row>
     <row r="23">
@@ -1154,18 +1442,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="n">
+        <v>0.05712291610208527</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0.1463826817873636</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.03734481050962286</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.0246600769296292</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.1308393266013442</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0.3192050653454921</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.07402914876404175</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0.1168143086254848</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.1115557965155378</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.2739369165660934</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.06336873304478369</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>0.08334479306525308</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1174,18 +1486,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="n">
+        <v>0.136870892613014</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.3052768291503663</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.0822153851789261</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.05895389258090319</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.2153900663555054</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.4625514485331905</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.133504335784233</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0.1697175122557019</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.1709316362264151</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0.3809981270216176</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0.1038241008753693</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.1188058728567992</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1199,40 +1535,40 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0</v>
+        <v>0.06478078567319875</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0</v>
+        <v>0.1549918381244351</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0</v>
+        <v>0.03410394580803185</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>0.03798926550776972</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0</v>
+        <v>0.1294721468969452</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0</v>
+        <v>0.2826654042428534</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0</v>
+        <v>0.06522895159938101</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
+        <v>0.07065706301330342</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>0.09820753119499791</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0</v>
+        <v>0.2222495118571442</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0</v>
+        <v>0.05021803590447078</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0</v>
+        <v>0.05524531261780655</v>
       </c>
     </row>
     <row r="26">
@@ -1242,18 +1578,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr"/>
+      <c r="C26" s="4" t="n">
+        <v>0.05245222598813972</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.1361204182236957</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.02668177138829405</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.03187222464967027</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.1168212302757333</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.2584065563941694</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0.05527979210226017</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>0.06257929192354673</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>0.08997322105965706</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0.2071471659038369</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>0.04451988548700433</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0.05007343311576538</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1262,18 +1622,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="n">
+        <v>0.07733161000638204</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0.1792808440022101</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.04291848959409758</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.04458281741491994</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.1433090696822057</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.306278688378803</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.07646761268272879</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>0.07878251863445818</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.1083042992759648</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0.2389476610532061</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0.05715000035678613</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0.06081091698757127</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1450,40 +1834,40 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -1494,40 +1878,40 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0</v>
+        <v>7347</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>6562</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>3917</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>1878</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>14541</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>17371</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>3782</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>1125</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>21888</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>23934</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>7699</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="6">
@@ -1537,18 +1921,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1648</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3847</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1498</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>855</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6579</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>12427</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1575</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>452</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>11301</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>18528</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>3922</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>1728</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -1557,18 +1965,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="n">
+        <v>20987</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>10772</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>8470</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3709</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>28572</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>22144</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>8213</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>2310</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>40420</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>30784</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>13694</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>5331</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1582,40 +2014,40 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1626,40 +2058,40 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0</v>
+        <v>6267</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>14930</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>5086</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>1215</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>22649</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
+        <v>32394</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>7187</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>1881</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0</v>
+        <v>28915</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0</v>
+        <v>47324</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0</v>
+        <v>12274</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="10">
@@ -1669,18 +2101,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>1687</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>10450</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2159</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>576</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>14269</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>25545</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3656</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>975</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>19172</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>38715</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>7442</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1978</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -1689,18 +2145,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>14947</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>20844</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9801</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>2413</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>34891</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>40070</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>12681</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>3266</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>43305</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>57333</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>18629</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>4948</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1714,40 +2194,40 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -1758,40 +2238,40 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>17232</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>23455</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>5806</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>1821</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>23571</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>28564</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0</v>
+        <v>13808</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0</v>
+        <v>3509</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0</v>
+        <v>40803</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0</v>
+        <v>52019</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0</v>
+        <v>19614</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="14">
@@ -1801,18 +2281,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n">
+        <v>9684</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>17400</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2430</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>914</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>16614</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>22235</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>8803</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>2245</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>30095</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>43296</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>13596</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>3632</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1821,18 +2325,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="n">
+        <v>29684</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>30596</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10879</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3299</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>33505</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>35647</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>20281</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>5286</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>55566</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>62616</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>28306</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>7672</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1846,40 +2374,40 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1890,40 +2418,40 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>34294</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>20749</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>5811</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>4662</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>53257</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>32921</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0</v>
+        <v>14733</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>6372</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0</v>
+        <v>87551</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>53670</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0</v>
+        <v>20544</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0</v>
+        <v>11033</v>
       </c>
     </row>
     <row r="18">
@@ -1933,18 +2461,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>23897</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>14963</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2984</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>43550</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>25971</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>9198</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>4550</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>70961</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>44797</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>13868</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>8568</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1953,18 +2505,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>48098</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>27194</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>10324</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>6777</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>65187</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>41535</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>22047</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>8956</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>104627</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>64350</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>29689</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>14072</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1978,40 +2554,40 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
@@ -2022,40 +2598,40 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>31659</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>12504</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>11853</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>7863</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>59211</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>34573</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0</v>
+        <v>18360</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0</v>
+        <v>11228</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0</v>
+        <v>90870</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>47077</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0</v>
+        <v>30212</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>19091</v>
       </c>
     </row>
     <row r="22">
@@ -2065,18 +2641,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>22969</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>8038</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>7002</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>5583</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>48646</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>27946</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>12725</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>8642</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>77430</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>38583</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>22036</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>15469</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -2085,18 +2685,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>43298</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>17470</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>18350</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>10548</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>70661</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>43017</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>26222</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>14341</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>106364</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>58032</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>40162</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>23168</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -2110,40 +2734,40 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -2154,40 +2778,40 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>6652</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>12621</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>3497</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0</v>
+        <v>4046</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0</v>
+        <v>38308</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0</v>
+        <v>24560</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0</v>
+        <v>12535</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0</v>
+        <v>9909</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0</v>
+        <v>44960</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0</v>
+        <v>37180</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0</v>
+        <v>16031</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0</v>
+        <v>13955</v>
       </c>
     </row>
     <row r="26">
@@ -2197,18 +2821,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="n">
+        <v>3196</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>8275</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1908</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>2669</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>31015</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>17809</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>8532</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>7613</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>35886</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>28917</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>11877</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>11069</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -2217,18 +2865,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
+        <v>12043</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>18832</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>6157</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>6146</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>46879</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>33087</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>17483</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>12858</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>55459</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>47160</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>21482</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>17159</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2242,40 +2914,40 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29">
@@ -2286,40 +2958,40 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0</v>
+        <v>13356</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0</v>
+        <v>14741</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>6776</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0</v>
+        <v>3123</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>38062</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0</v>
+        <v>43935</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0</v>
+        <v>17362</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0</v>
+        <v>17222</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0</v>
+        <v>51418</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0</v>
+        <v>58676</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0</v>
+        <v>24138</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0</v>
+        <v>20346</v>
       </c>
     </row>
     <row r="30">
@@ -2329,18 +3001,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>8183</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>10101</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>4452</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>29193</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>36377</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>13133</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>14271</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>40871</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>50121</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>18796</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>17075</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -2349,18 +3045,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
+        <v>19607</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>21066</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>9801</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>4875</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>48058</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>52712</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>23684</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>20735</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>62625</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>69710</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>30796</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>24340</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2374,40 +3094,40 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33">
@@ -2418,40 +3138,40 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0</v>
+        <v>116807</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0</v>
+        <v>105562</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>42746</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0</v>
+        <v>24608</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0</v>
+        <v>249598</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0</v>
+        <v>214319</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0</v>
+        <v>87766</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0</v>
+        <v>51246</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0</v>
+        <v>366406</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0</v>
+        <v>319881</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0</v>
+        <v>130512</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0</v>
+        <v>75854</v>
       </c>
     </row>
     <row r="34">
@@ -2461,18 +3181,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr"/>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="n">
+        <v>94578</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>92709</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>33443</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>20645</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>225210</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>195926</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>74380</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>45387</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>335684</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>298145</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>115703</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>68752</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -2481,18 +3225,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="n">
+        <v>139438</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>122105</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>53794</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>28879</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>276273</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>232223</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>102888</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>57139</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>404076</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>343915</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>148528</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>83495</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
